--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_silicon/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_silicon.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_silicon/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_silicon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11334,12 +11334,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12478,12 +12478,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12738,12 +12738,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
